--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -6586,7 +6586,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J145" t="n">
         <v>1</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
@@ -6970,10 +6970,10 @@
         <v>0.994961</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
@@ -7013,10 +7013,10 @@
         <v>0.235543</v>
       </c>
       <c r="H153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J153" t="n">
         <v>1</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J166" t="n">
         <v>1</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
         <v>1</v>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
         <v>1</v>
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J190" t="n">
         <v>1</v>
@@ -8650,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J191" t="n">
         <v>1</v>
@@ -9209,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -10410,10 +10410,10 @@
         <v>0.363337</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -11058,7 +11058,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J247" t="n">
         <v>1</v>
@@ -11273,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J252" t="n">
         <v>1</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="I277" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -12778,7 +12778,7 @@
         <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J287" t="n">
         <v>1</v>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="I289" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -13162,10 +13162,10 @@
         <v>0.986838</v>
       </c>
       <c r="H296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I296" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J296" t="n">
         <v>1</v>
@@ -13721,10 +13721,10 @@
         <v>0.75366</v>
       </c>
       <c r="H309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J309" t="n">
         <v>0</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.342079</v>
+        <v>0.203793</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.181965</v>
+        <v>0.105458</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.169242</v>
+        <v>0.080803</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.993166</v>
+        <v>0.999692</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.138605</v>
+        <v>0.08335099999999999</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.908681</v>
+        <v>0.9480420000000001</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.174471</v>
+        <v>0.09367200000000001</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.189667</v>
+        <v>0.094402</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.244691</v>
+        <v>0.132817</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.245848</v>
+        <v>0.101822</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.356717</v>
+        <v>0.161779</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.295803</v>
+        <v>0.154781</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0.004887</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.531507</v>
+        <v>0.23687</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.231807</v>
+        <v>0.104806</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.845194</v>
+        <v>0.72115</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.169923</v>
+        <v>0.07974100000000001</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.47462</v>
+        <v>0.30585</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.899992</v>
+        <v>0.845217</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.624347</v>
+        <v>0.545054</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.220313</v>
+        <v>0.104441</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.192979</v>
+        <v>0.085411</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.245873</v>
+        <v>0.107936</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.141736</v>
+        <v>0.06460200000000001</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.225891</v>
+        <v>0.111291</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.8416709999999999</v>
+        <v>0.92758</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6018,10 +6018,10 @@
         <v>0.041172</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.457391</v>
+        <v>0.596132</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.260441</v>
+        <v>0.121114</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.268677</v>
+        <v>0.112816</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.249184</v>
+        <v>0.08556800000000001</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.396374</v>
+        <v>0.194295</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.244272</v>
+        <v>0.167924</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.243997</v>
+        <v>0.093635</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.203903</v>
+        <v>0.098888</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.189566</v>
+        <v>0.077957</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.32752</v>
+        <v>0.177477</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.189391</v>
+        <v>0.086254</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.349944</v>
+        <v>0.186651</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.231746</v>
+        <v>0.116398</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.323157</v>
+        <v>0.158105</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.35945</v>
+        <v>0.18935</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.277619</v>
+        <v>0.118402</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.322234</v>
+        <v>0.207964</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.304343</v>
+        <v>0.224178</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.15791</v>
+        <v>0.08144999999999999</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.462233</v>
+        <v>0.31304</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.23981</v>
+        <v>0.110819</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.953564</v>
+        <v>0.96562</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.994961</v>
+        <v>0.9997</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.235543</v>
+        <v>0.152877</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7050,10 +7050,10 @@
         <v>0.000616</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.768984</v>
+        <v>0.434166</v>
       </c>
       <c r="H154" t="n">
         <v>1</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.324284</v>
+        <v>0.238887</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.253965</v>
+        <v>0.13477</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.310133</v>
+        <v>0.252183</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.245881</v>
+        <v>0.139732</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.186072</v>
+        <v>0.09535299999999999</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.179471</v>
+        <v>0.128755</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.12184</v>
+        <v>0.07013999999999999</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.225606</v>
+        <v>0.145259</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7437,10 +7437,10 @@
         <v>5e-06</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.568454</v>
+        <v>0.300752</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.189965</v>
+        <v>0.192345</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.15515</v>
+        <v>0.11914</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.476295</v>
+        <v>0.369655</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.131058</v>
+        <v>0.062556</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.434122</v>
+        <v>0.303867</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.172048</v>
+        <v>0.099844</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.127374</v>
+        <v>0.09239700000000001</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.228591</v>
+        <v>0.153503</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.478854</v>
+        <v>0.214423</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.131552</v>
+        <v>0.059375</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.120203</v>
+        <v>0.060387</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.184102</v>
+        <v>0.111582</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.280434</v>
+        <v>0.169596</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.192258</v>
+        <v>0.077497</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.16505</v>
+        <v>0.089035</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.233341</v>
+        <v>0.09997200000000001</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.236511</v>
+        <v>0.095079</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.310155</v>
+        <v>0.151622</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8254,10 +8254,10 @@
         <v>0.006986</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.535561</v>
+        <v>0.300429</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.231955</v>
+        <v>0.095848</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.277999</v>
+        <v>0.144625</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.335346</v>
+        <v>0.215478</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.281255</v>
+        <v>0.140146</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.30837</v>
+        <v>0.132042</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.308314</v>
+        <v>0.196068</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.215176</v>
+        <v>0.114401</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8598,10 +8598,10 @@
         <v>0.08533499999999999</v>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0.71894</v>
+        <v>0.493495</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.488734</v>
+        <v>0.344702</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.449401</v>
+        <v>0.424203</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8727,10 +8727,10 @@
         <v>0.003362</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" t="n">
-        <v>0.404223</v>
+        <v>0.505598</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.224498</v>
+        <v>0.159161</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.274538</v>
+        <v>0.170569</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.276348</v>
+        <v>0.178263</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.947983</v>
+        <v>0.984874</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.703716</v>
+        <v>0.734752</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.7173659999999999</v>
+        <v>0.627158</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.315971</v>
+        <v>0.164341</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.21235</v>
+        <v>0.135016</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.08824899999999999</v>
+        <v>0.109813</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.169376</v>
+        <v>0.160891</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.293828</v>
+        <v>0.337619</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.097486</v>
+        <v>0.087899</v>
       </c>
       <c r="H317" t="n">
         <v>1</v>
@@ -14102,10 +14102,10 @@
         <v>0.053126</v>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.724177</v>
+        <v>0.437975</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14145,10 +14145,10 @@
         <v>2.2e-05</v>
       </c>
       <c r="F319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.576745</v>
+        <v>0.387619</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14188,10 +14188,10 @@
         <v>2e-06</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>0.628914</v>
+        <v>0.265644</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.128722</v>
+        <v>0.108108</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.179774</v>
+        <v>0.163372</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.132136</v>
+        <v>0.06844</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.231886</v>
+        <v>0.156512</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.131461</v>
+        <v>0.07706399999999999</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.159544</v>
+        <v>0.078199</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.288009</v>
+        <v>0.147575</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.907193</v>
+        <v>0.777687</v>
       </c>
       <c r="H328" t="n">
         <v>1</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.155268</v>
+        <v>0.128659</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.118763</v>
+        <v>0.091266</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.986354</v>
+        <v>0.992279</v>
       </c>
       <c r="H331" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.119083</v>
+        <v>0.08881500000000001</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.991754</v>
+        <v>0.997438</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.490801</v>
+        <v>0.430909</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.179093</v>
+        <v>0.147382</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.120715</v>
+        <v>0.127033</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.091545</v>
+        <v>0.057754</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.136922</v>
+        <v>0.09529700000000001</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.129829</v>
+        <v>0.08383599999999999</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.190319</v>
+        <v>0.128255</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.146234</v>
+        <v>0.099926</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.106594</v>
+        <v>0.081223</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.1113</v>
+        <v>0.08424</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.0648</v>
+        <v>0.067622</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.174885</v>
+        <v>0.13022</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.238161</v>
+        <v>0.290646</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.142208</v>
+        <v>0.092428</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0.724929</v>
+        <v>0.635843</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0.788918</v>
+        <v>0.560859</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.7012119999999999</v>
+        <v>0.87653</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15521,10 +15521,10 @@
         <v>0.023686</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.509942</v>
+        <v>0.389673</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.270792</v>
+        <v>0.209059</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.127139</v>
+        <v>0.077907</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.132639</v>
+        <v>0.120819</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.06883400000000001</v>
+        <v>0.046881</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.082051</v>
+        <v>0.062907</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.145984</v>
+        <v>0.084965</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0.284014</v>
+        <v>0.185558</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.073042</v>
+        <v>0.050857</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.75784</v>
+        <v>0.647452</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0.6723479999999999</v>
+        <v>0.711152</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.993269</v>
+        <v>0.996315</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.091294</v>
+        <v>0.08937</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.971882</v>
+        <v>0.987035</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.158649</v>
+        <v>0.183521</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.227656</v>
+        <v>0.135943</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0.57605</v>
+        <v>0.649181</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.31324</v>
+        <v>0.16126</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.391973</v>
+        <v>0.280813</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.157681</v>
+        <v>0.131263</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0.9250389999999999</v>
+        <v>0.973502</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.15335</v>
+        <v>0.148415</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.133355</v>
+        <v>0.149532</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.186146</v>
+        <v>0.136674</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.306868</v>
+        <v>0.189716</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.161042</v>
+        <v>0.13752</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.177158</v>
+        <v>0.109368</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.48429</v>
+        <v>0.365729</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.479109</v>
+        <v>0.325674</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.695585</v>
+        <v>0.700466</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.46569</v>
+        <v>0.406264</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>1</v>
       </c>
       <c r="G382" t="n">
-        <v>0.5071369999999999</v>
+        <v>0.519356</v>
       </c>
       <c r="H382" t="n">
         <v>1</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.040199</v>
+        <v>0.047919</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.132685</v>
+        <v>0.116705</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.039602</v>
+        <v>0.050484</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.065165</v>
+        <v>0.07203900000000001</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.311245</v>
+        <v>0.178442</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.309256</v>
+        <v>0.160817</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.086572</v>
+        <v>0.09161999999999999</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.296475</v>
+        <v>0.265753</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.441132</v>
+        <v>0.285661</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.44269</v>
+        <v>0.326756</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.653174</v>
+        <v>0.76172</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.121879</v>
+        <v>0.096715</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.569159</v>
+        <v>0.525855</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.284743</v>
+        <v>0.205222</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.715203</v>
+        <v>0.512817</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.327875</v>
+        <v>0.271873</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.173363</v>
+        <v>0.135245</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.228913</v>
+        <v>0.146832</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.438685</v>
+        <v>0.22119</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.134064</v>
+        <v>0.09225</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.956232</v>
+        <v>0.966996</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.13514</v>
+        <v>0.090141</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.076851</v>
+        <v>0.081543</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.199564</v>
+        <v>0.129525</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.72009</v>
+        <v>0.502328</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.996569</v>
+        <v>0.998541</v>
       </c>
       <c r="H408" t="n">
         <v>1</v>
@@ -18015,10 +18015,10 @@
         <v>0</v>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.545017</v>
+        <v>0.46987</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.08864</v>
+        <v>0.068637</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18101,10 +18101,10 @@
         <v>2e-06</v>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0.637426</v>
+        <v>0.330858</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18144,10 +18144,10 @@
         <v>1e-05</v>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.665535</v>
+        <v>0.268189</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.152039</v>
+        <v>0.095802</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.85851</v>
+        <v>0.644962</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
